--- a/samples/Payslip_Template.xlsx
+++ b/samples/Payslip_Template.xlsx
@@ -399,11 +399,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="2" max="2" width="44.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,9 +549,31 @@
         <v>Optional. Free text printed at the bottom of each payslip. Example: This is a system-generated payslip and does not require a signature.</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Logo</v>
+      </c>
+      <c r="B14" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Stamp / Signature</v>
+      </c>
+      <c r="B15" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Optional. The second picture on this sheet is used as the stamp or signature.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -743,7 +765,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -768,85 +790,76 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2. Fill the "Payslips" sheet with one row per employee. Delete the example row.</v>
+        <v>2. Optional: insert your logo picture on the "Settings" sheet (Insert &gt; Pictures). A second picture is used as stamp/signature.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. Keep the header row exactly as it is. You may delete optional columns you do not use.</v>
+        <v>3. Fill the "Payslips" sheet with one row per employee. Delete the example row.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>4. Amounts must be numbers (no text). Leave a cell empty for zero.</v>
+        <v>4. Keep the header row. You may delete optional columns you do not use, and reorder columns freely.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>5. Extra pay items: add a column named "Earning: &lt;name&gt;" (e.g. "Earning: Site Allowance").</v>
+        <v>5. Amounts must be numbers (no text). Leave a cell empty for zero.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>6. Extra deductions: add a column named "Deduction: &lt;name&gt;" (e.g. "Deduction: Housing Loan").</v>
+        <v>6. Extra pay items: add a column named "Earning: &lt;name&gt;" (e.g. "Earning: Site Allowance").</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>7. Net Salary is calculated automatically (earnings - deductions). If you fill the Net Salary column it is only used as a cross-check.</v>
+        <v>7. Extra deductions: add a column named "Deduction: &lt;name&gt;" (e.g. "Deduction: Housing Loan").</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>8. Save the file, open the Payslip Generator page, upload this file, review the checks, pick a design and export the PDFs.</v>
+        <v>8. Net Salary is calculated automatically (earnings - deductions). If you fill the Net Salary column it is only used as a cross-check.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>9. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
+        <v>9. Save the file, open the Payslip Generator page, upload this file, review the checks, pick a design and export the PDFs.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>10. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>COLUMNS</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Column</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Required</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Group</v>
+        <v>COLUMNS</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Employee ID</v>
+        <v>Column</v>
       </c>
       <c r="B15" t="str">
-        <v>Yes</v>
+        <v>Required</v>
       </c>
       <c r="C15" t="str">
-        <v>text</v>
+        <v>Type</v>
       </c>
       <c r="D15" t="str">
-        <v>info</v>
+        <v>Group</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Employee Name</v>
+        <v>Employee ID</v>
       </c>
       <c r="B16" t="str">
         <v>Yes</v>
@@ -860,10 +873,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>National ID / Iqama</v>
+        <v>Employee Name</v>
       </c>
       <c r="B17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C17" t="str">
         <v>text</v>
@@ -874,7 +887,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Nationality</v>
+        <v>National ID / Iqama</v>
       </c>
       <c r="B18" t="str">
         <v>No</v>
@@ -888,7 +901,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Job Title</v>
+        <v>Nationality</v>
       </c>
       <c r="B19" t="str">
         <v>No</v>
@@ -902,7 +915,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Department</v>
+        <v>Job Title</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
@@ -916,13 +929,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Joining Date</v>
+        <v>Department</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
       </c>
       <c r="C21" t="str">
-        <v>date</v>
+        <v>text</v>
       </c>
       <c r="D21" t="str">
         <v>info</v>
@@ -930,13 +943,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Bank Name</v>
+        <v>Joining Date</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D22" t="str">
         <v>info</v>
@@ -944,7 +957,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>IBAN</v>
+        <v>Bank Name</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
@@ -958,21 +971,21 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Working Days</v>
+        <v>IBAN</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D24" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Absent Days</v>
+        <v>Working Days</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
@@ -986,7 +999,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Overtime Hours</v>
+        <v>Absent Days</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
@@ -1000,24 +1013,24 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Basic Salary</v>
+        <v>Overtime Hours</v>
       </c>
       <c r="B27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D27" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Housing Allowance</v>
+        <v>Basic Salary</v>
       </c>
       <c r="B28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C28" t="str">
         <v>money</v>
@@ -1028,7 +1041,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Transport Allowance</v>
+        <v>Housing Allowance</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
@@ -1042,7 +1055,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Food Allowance</v>
+        <v>Transport Allowance</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
@@ -1056,7 +1069,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Overtime Pay</v>
+        <v>Food Allowance</v>
       </c>
       <c r="B31" t="str">
         <v>No</v>
@@ -1070,7 +1083,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Other Earnings</v>
+        <v>Overtime Pay</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1084,7 +1097,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GOSI Deduction</v>
+        <v>Other Earnings</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1093,12 +1106,12 @@
         <v>money</v>
       </c>
       <c r="D33" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Absence Deduction</v>
+        <v>GOSI Deduction</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1112,7 +1125,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Loan / Advance</v>
+        <v>Absence Deduction</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1126,7 +1139,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Other Deductions</v>
+        <v>Loan / Advance</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1140,7 +1153,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Net Salary</v>
+        <v>Other Deductions</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1149,26 +1162,40 @@
         <v>money</v>
       </c>
       <c r="D37" t="str">
-        <v>check</v>
+        <v>deduction</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
+        <v>Net Salary</v>
+      </c>
+      <c r="B38" t="str">
+        <v>No</v>
+      </c>
+      <c r="C38" t="str">
+        <v>money</v>
+      </c>
+      <c r="D38" t="str">
+        <v>check</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>Remarks</v>
       </c>
-      <c r="B38" t="str">
-        <v>No</v>
-      </c>
-      <c r="C38" t="str">
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+      <c r="C39" t="str">
         <v>text</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D39" t="str">
         <v>info</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Payslip_Template.xlsx
+++ b/samples/Payslip_Template.xlsx
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>10. Use English/Latin letters for names and text. Arabic script is not supported by the PDF fonts in this version.</v>
+        <v>10. Names and text can be in English or Arabic (or both).</v>
       </c>
     </row>
     <row r="13">

--- a/samples/Payslip_Template.xlsx
+++ b/samples/Payslip_Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" customWidth="1"/>
@@ -551,61 +551,122 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Logo</v>
+        <v>Default Country Code</v>
       </c>
       <c r="B14" t="str">
-        <v>(optional: insert the picture anywhere on this sheet)</v>
+        <v>966</v>
       </c>
       <c r="C14" t="str">
-        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+        <v>Optional. Added to mobile numbers written without a country code (966 = Saudi Arabia). Example: 966</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Sender Email</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>Optional. The From address used in Outlook drafts and mail-merge files. Example: payroll@example.com</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Message Subject</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Payslip {period} - {company}</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Optional. Subject line for emails and first line of WhatsApp messages. Placeholders: {name} {period} {company} {net} {password_hint} Example: Payslip {period} - {company}</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>Message Text</v>
+      </c>
+      <c r="B17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear {name}, your payslip for {period} is attached. {password_hint}
+This document contains personal data; please do not forward it.
+عزيزي {name}، مرفق قسيمة راتبك لشهر {period}. {password_hint_ar}
+هذا المستند يحتوي على بيانات شخصية، يرجى عدم مشاركته.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Password Rule</v>
+      </c>
+      <c r="B18" t="str">
+        <v>id+dob</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Optional. How each PDF password is built: none, id (National ID / Iqama), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column). Example: id+dob</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Logo</v>
+      </c>
+      <c r="B19" t="str">
+        <v>(optional: insert the picture anywhere on this sheet)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Optional. Insert your logo picture anywhere on this sheet (Insert &gt; Pictures). The first picture on this sheet is used as the logo.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>Stamp / Signature</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B20" t="str">
         <v>(optional: insert the picture anywhere on this sheet)</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C20" t="str">
         <v>Optional. The second picture on this sheet is used as the stamp or signature.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AA2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="21.83203125" customWidth="1"/>
-    <col min="16" max="16" width="16.83203125" customWidth="1"/>
-    <col min="17" max="17" width="14.83203125" customWidth="1"/>
-    <col min="18" max="18" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="19.83203125" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" customWidth="1"/>
     <col min="19" max="19" width="16.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
     <col min="21" max="21" width="16.83203125" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="16.83203125" customWidth="1"/>
+    <col min="23" max="23" width="19.83203125" customWidth="1"/>
+    <col min="24" max="24" width="16.83203125" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -622,63 +683,72 @@
         <v>Nationality</v>
       </c>
       <c r="E1" t="str">
+        <v>Date of Birth</v>
+      </c>
+      <c r="F1" t="str">
         <v>Job Title</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Department</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Joining Date</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>Mobile</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="K1" t="str">
         <v>Bank Name</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>IBAN</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Working Days</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Absent Days</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>Overtime Hours</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Basic Salary</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Housing Allowance</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Transport Allowance</v>
       </c>
-      <c r="P1" t="str">
+      <c r="S1" t="str">
         <v>Food Allowance</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <v>Overtime Pay</v>
       </c>
-      <c r="R1" t="str">
+      <c r="U1" t="str">
         <v>Other Earnings</v>
       </c>
-      <c r="S1" t="str">
+      <c r="V1" t="str">
         <v>GOSI Deduction</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
         <v>Absence Deduction</v>
       </c>
-      <c r="U1" t="str">
+      <c r="X1" t="str">
         <v>Loan / Advance</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Y1" t="str">
         <v>Other Deductions</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <v>Net Salary</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <v>Remarks</v>
       </c>
     </row>
@@ -696,52 +766,52 @@
         <v>Egyptian</v>
       </c>
       <c r="E2" t="str">
+        <v>1990-03-15</v>
+      </c>
+      <c r="F2" t="str">
         <v>Site Engineer</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Projects</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>2024-03-15</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v>0551234567</v>
+      </c>
+      <c r="J2" t="str">
+        <v>ahmed@example.com</v>
+      </c>
+      <c r="K2" t="str">
         <v>Al Rajhi Bank</v>
       </c>
-      <c r="I2" t="str">
+      <c r="L2" t="str">
         <v>SA0380000000608010167519</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>30</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>10</v>
       </c>
-      <c r="M2">
+      <c r="P2">
         <v>4000</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>1000</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>400</v>
       </c>
-      <c r="P2">
+      <c r="S2">
         <v>300</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>250</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -749,23 +819,32 @@
       <c r="V2">
         <v>0</v>
       </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D42"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -915,13 +994,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Job Title</v>
+        <v>Date of Birth</v>
       </c>
       <c r="B20" t="str">
         <v>No</v>
       </c>
       <c r="C20" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D20" t="str">
         <v>info</v>
@@ -929,7 +1008,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Department</v>
+        <v>Job Title</v>
       </c>
       <c r="B21" t="str">
         <v>No</v>
@@ -943,13 +1022,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Joining Date</v>
+        <v>Department</v>
       </c>
       <c r="B22" t="str">
         <v>No</v>
       </c>
       <c r="C22" t="str">
-        <v>date</v>
+        <v>text</v>
       </c>
       <c r="D22" t="str">
         <v>info</v>
@@ -957,13 +1036,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Bank Name</v>
+        <v>Joining Date</v>
       </c>
       <c r="B23" t="str">
         <v>No</v>
       </c>
       <c r="C23" t="str">
-        <v>text</v>
+        <v>date</v>
       </c>
       <c r="D23" t="str">
         <v>info</v>
@@ -971,108 +1050,108 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>IBAN</v>
+        <v>Mobile</v>
       </c>
       <c r="B24" t="str">
         <v>No</v>
       </c>
       <c r="C24" t="str">
-        <v>text</v>
+        <v>phone</v>
       </c>
       <c r="D24" t="str">
-        <v>info</v>
+        <v>contact</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Working Days</v>
+        <v>Email</v>
       </c>
       <c r="B25" t="str">
         <v>No</v>
       </c>
       <c r="C25" t="str">
-        <v>number</v>
+        <v>email</v>
       </c>
       <c r="D25" t="str">
-        <v>attendance</v>
+        <v>contact</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Absent Days</v>
+        <v>Bank Name</v>
       </c>
       <c r="B26" t="str">
         <v>No</v>
       </c>
       <c r="C26" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D26" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Overtime Hours</v>
+        <v>IBAN</v>
       </c>
       <c r="B27" t="str">
         <v>No</v>
       </c>
       <c r="C27" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="D27" t="str">
-        <v>attendance</v>
+        <v>info</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Basic Salary</v>
+        <v>Working Days</v>
       </c>
       <c r="B28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="C28" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D28" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Housing Allowance</v>
+        <v>Absent Days</v>
       </c>
       <c r="B29" t="str">
         <v>No</v>
       </c>
       <c r="C29" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D29" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Transport Allowance</v>
+        <v>Overtime Hours</v>
       </c>
       <c r="B30" t="str">
         <v>No</v>
       </c>
       <c r="C30" t="str">
-        <v>money</v>
+        <v>number</v>
       </c>
       <c r="D30" t="str">
-        <v>earning</v>
+        <v>attendance</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Food Allowance</v>
+        <v>Basic Salary</v>
       </c>
       <c r="B31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="C31" t="str">
         <v>money</v>
@@ -1083,7 +1162,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Overtime Pay</v>
+        <v>Housing Allowance</v>
       </c>
       <c r="B32" t="str">
         <v>No</v>
@@ -1097,7 +1176,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Other Earnings</v>
+        <v>Transport Allowance</v>
       </c>
       <c r="B33" t="str">
         <v>No</v>
@@ -1111,7 +1190,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GOSI Deduction</v>
+        <v>Food Allowance</v>
       </c>
       <c r="B34" t="str">
         <v>No</v>
@@ -1120,12 +1199,12 @@
         <v>money</v>
       </c>
       <c r="D34" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Absence Deduction</v>
+        <v>Overtime Pay</v>
       </c>
       <c r="B35" t="str">
         <v>No</v>
@@ -1134,12 +1213,12 @@
         <v>money</v>
       </c>
       <c r="D35" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Loan / Advance</v>
+        <v>Other Earnings</v>
       </c>
       <c r="B36" t="str">
         <v>No</v>
@@ -1148,12 +1227,12 @@
         <v>money</v>
       </c>
       <c r="D36" t="str">
-        <v>deduction</v>
+        <v>earning</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Other Deductions</v>
+        <v>GOSI Deduction</v>
       </c>
       <c r="B37" t="str">
         <v>No</v>
@@ -1167,7 +1246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Net Salary</v>
+        <v>Absence Deduction</v>
       </c>
       <c r="B38" t="str">
         <v>No</v>
@@ -1176,26 +1255,68 @@
         <v>money</v>
       </c>
       <c r="D38" t="str">
-        <v>check</v>
+        <v>deduction</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
+        <v>Loan / Advance</v>
+      </c>
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+      <c r="C39" t="str">
+        <v>money</v>
+      </c>
+      <c r="D39" t="str">
+        <v>deduction</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Other Deductions</v>
+      </c>
+      <c r="B40" t="str">
+        <v>No</v>
+      </c>
+      <c r="C40" t="str">
+        <v>money</v>
+      </c>
+      <c r="D40" t="str">
+        <v>deduction</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Net Salary</v>
+      </c>
+      <c r="B41" t="str">
+        <v>No</v>
+      </c>
+      <c r="C41" t="str">
+        <v>money</v>
+      </c>
+      <c r="D41" t="str">
+        <v>check</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
         <v>Remarks</v>
       </c>
-      <c r="B39" t="str">
-        <v>No</v>
-      </c>
-      <c r="C39" t="str">
+      <c r="B42" t="str">
+        <v>No</v>
+      </c>
+      <c r="C42" t="str">
         <v>text</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D42" t="str">
         <v>info</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/Payslip_Template.xlsx
+++ b/samples/Payslip_Template.xlsx
@@ -587,10 +587,10 @@
         <v>Message Text</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear {name}, your payslip for {period} is attached. {password_hint}
-This document contains personal data; please do not forward it.
-عزيزي {name}، مرفق قسيمة راتبك لشهر {period}. {password_hint_ar}
-هذا المستند يحتوي على بيانات شخصية، يرجى عدم مشاركته.</v>
+        <v xml:space="preserve">Dear {name},
+Please find attached your payslip for {period}.
+{password_hint}
+{company}</v>
       </c>
       <c r="C17" t="str">
         <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
@@ -601,10 +601,10 @@
         <v>Password Rule</v>
       </c>
       <c r="B18" t="str">
-        <v>id+dob</v>
+        <v>id</v>
       </c>
       <c r="C18" t="str">
-        <v>Optional. How each PDF password is built: none, id (National ID / Iqama), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column). Example: id+dob</v>
+        <v>Optional. PDF password: id (National ID / Iqama number, default), id+dob (ID + birth day and month DDMM), dob (DDMMYYYY), custom (uses the "Payslip Password" column), none. Example: id</v>
       </c>
     </row>
     <row r="19">

--- a/samples/Payslip_Template.xlsx
+++ b/samples/Payslip_Template.xlsx
@@ -587,13 +587,13 @@
         <v>Message Text</v>
       </c>
       <c r="B17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Dear {name},
+        <v xml:space="preserve">Dear {first_name},
 Please find attached your payslip for {period}.
 {password_hint}
-{company}</v>
+Best regards</v>
       </c>
       <c r="C17" t="str">
-        <v>Optional. Body of the email / WhatsApp message. Placeholders: {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
+        <v>Optional. Body of the email / WhatsApp message. Placeholders: {first_name} {name} {period} {company} {net} {password_hint} {password_hint_ar}</v>
       </c>
     </row>
     <row r="18">
